--- a/docs/design/ACSMS-SCR-020/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_口座振替データ出力画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-020/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_口座振替データ出力画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1363,20 +1363,136 @@
       <c r="AG2" s="10" t="n"/>
       <c r="AH2" s="11" t="n"/>
     </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="18" t="inlineStr"/>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>2026/07/11</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>VTI Japan</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>v1.1対応：カテゴリ6（プレビュー→金額編集→ファイル作成）を追加（TC-048〜055）。</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="19" t="inlineStr"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="19" t="inlineStr"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="18" t="inlineStr"/>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="11" t="n"/>
+      <c r="O4" s="20" t="inlineStr">
+        <is>
+          <t>実装との差分補完：カテゴリ7を新設し2件追加（TC-056〜057）。056＝集計対象を紙版と「承認済かつ有料」の電子版のみに限定し併読を除外する条件（顧客要件2026-08 / #56600・API設計書 v1.2）。057＝失効単価(`active_flg=false`)参照時の出力ブロック（HTTP 409 `INACTIVE_TANKA_REFERENCED`・`errors[]` 先頭15件打ち切りと `total`・API設計書 v1.1）。いずれも本書 v1.1（2026/07/11）より後に入った仕様で未反映だった</t>
+        </is>
+      </c>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="11" t="n"/>
+      <c r="W4" s="19" t="inlineStr"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="11" t="n"/>
+      <c r="AC4" s="19" t="inlineStr"/>
+      <c r="AD4" s="10" t="n"/>
+      <c r="AE4" s="10" t="n"/>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="10" t="n"/>
+      <c r="AH4" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="24">
+    <mergeCell ref="O3:V3"/>
+    <mergeCell ref="W1:AB1"/>
+    <mergeCell ref="W3:AB3"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="AC4:AH4"/>
+    <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="O1:V1"/>
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC2:AH2"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="W4:AB4"/>
     <mergeCell ref="B1:E1"/>
-    <mergeCell ref="AC2:AH2"/>
-    <mergeCell ref="AC1:AH1"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
-    <mergeCell ref="W1:AB1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="O1:V1"/>
-    <mergeCell ref="I1:N1"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC3:AH3"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6239,7 +6355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ63"/>
+  <dimension ref="A1:BQ75"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -15626,8 +15742,1971 @@
       <c r="BP63" s="10" t="n"/>
       <c r="BQ63" s="11" t="n"/>
     </row>
+    <row r="64" ht="22.5" customHeight="1">
+      <c r="A64" s="32" t="inlineStr">
+        <is>
+          <t>カテゴリ6: v1.1 プレビュー→金額編集→ファイル作成（Preview / Edit / Make File）</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="10" t="n"/>
+      <c r="E64" s="10" t="n"/>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
+      <c r="H64" s="10" t="n"/>
+      <c r="I64" s="10" t="n"/>
+      <c r="J64" s="10" t="n"/>
+      <c r="K64" s="10" t="n"/>
+      <c r="L64" s="10" t="n"/>
+      <c r="M64" s="10" t="n"/>
+      <c r="N64" s="10" t="n"/>
+      <c r="O64" s="10" t="n"/>
+      <c r="P64" s="10" t="n"/>
+      <c r="Q64" s="10" t="n"/>
+      <c r="R64" s="10" t="n"/>
+      <c r="S64" s="10" t="n"/>
+      <c r="T64" s="10" t="n"/>
+      <c r="U64" s="10" t="n"/>
+      <c r="V64" s="10" t="n"/>
+      <c r="W64" s="10" t="n"/>
+      <c r="X64" s="10" t="n"/>
+      <c r="Y64" s="10" t="n"/>
+      <c r="Z64" s="10" t="n"/>
+      <c r="AA64" s="10" t="n"/>
+      <c r="AB64" s="10" t="n"/>
+      <c r="AC64" s="10" t="n"/>
+      <c r="AD64" s="10" t="n"/>
+      <c r="AE64" s="10" t="n"/>
+      <c r="AF64" s="10" t="n"/>
+      <c r="AG64" s="10" t="n"/>
+      <c r="AH64" s="10" t="n"/>
+      <c r="AI64" s="10" t="n"/>
+      <c r="AJ64" s="10" t="n"/>
+      <c r="AK64" s="10" t="n"/>
+      <c r="AL64" s="10" t="n"/>
+      <c r="AM64" s="10" t="n"/>
+      <c r="AN64" s="10" t="n"/>
+      <c r="AO64" s="10" t="n"/>
+      <c r="AP64" s="10" t="n"/>
+      <c r="AQ64" s="10" t="n"/>
+      <c r="AR64" s="10" t="n"/>
+      <c r="AS64" s="10" t="n"/>
+      <c r="AT64" s="10" t="n"/>
+      <c r="AU64" s="10" t="n"/>
+      <c r="AV64" s="10" t="n"/>
+      <c r="AW64" s="10" t="n"/>
+      <c r="AX64" s="10" t="n"/>
+      <c r="AY64" s="10" t="n"/>
+      <c r="AZ64" s="10" t="n"/>
+      <c r="BA64" s="10" t="n"/>
+      <c r="BB64" s="10" t="n"/>
+      <c r="BC64" s="10" t="n"/>
+      <c r="BD64" s="10" t="n"/>
+      <c r="BE64" s="10" t="n"/>
+      <c r="BF64" s="10" t="n"/>
+      <c r="BG64" s="10" t="n"/>
+      <c r="BH64" s="10" t="n"/>
+      <c r="BI64" s="10" t="n"/>
+      <c r="BJ64" s="10" t="n"/>
+      <c r="BK64" s="10" t="n"/>
+      <c r="BL64" s="10" t="n"/>
+      <c r="BM64" s="10" t="n"/>
+      <c r="BN64" s="10" t="n"/>
+      <c r="BO64" s="10" t="n"/>
+      <c r="BP64" s="10" t="n"/>
+      <c r="BQ64" s="11" t="n"/>
+    </row>
+    <row r="65" ht="208" customHeight="1">
+      <c r="A65" s="44" t="n">
+        <v>48</v>
+      </c>
+      <c r="B65" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-020-048</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="n"/>
+      <c r="D65" s="11" t="n"/>
+      <c r="E65" s="46" t="inlineStr">
+        <is>
+          <t>作成開始でプレビュー一覧を表示（ファイル出力しない）</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="n"/>
+      <c r="G65" s="10" t="n"/>
+      <c r="H65" s="10" t="n"/>
+      <c r="I65" s="11" t="n"/>
+      <c r="J65" s="46" t="inlineStr">
+        <is>
+          <t>・CHUOKAI でログイン済み
+・対象年月に集計対象の購読者が存在する</t>
+        </is>
+      </c>
+      <c r="K65" s="10" t="n"/>
+      <c r="L65" s="10" t="n"/>
+      <c r="M65" s="10" t="n"/>
+      <c r="N65" s="10" t="n"/>
+      <c r="O65" s="10" t="n"/>
+      <c r="P65" s="11" t="n"/>
+      <c r="Q65" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>年月日・引落日を入力して「作成開始」を実行する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R65" s="10" t="n"/>
+      <c r="S65" s="10" t="n"/>
+      <c r="T65" s="10" t="n"/>
+      <c r="U65" s="10" t="n"/>
+      <c r="V65" s="10" t="n"/>
+      <c r="W65" s="11" t="n"/>
+      <c r="X65" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・POST /api/v1/koza-furikae/preview が呼ばれ、200 で `{ data, meta }` が返ること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・プレビュー一覧表（預金者名／引落支店／口座番号／金額）が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・「ファイル作成」ボタンが表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・**この時点でファイルはダウンロードされず、S3保存・t_koza_furikae更新・監査ログも行われないこと**</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y65" s="10" t="n"/>
+      <c r="Z65" s="10" t="n"/>
+      <c r="AA65" s="10" t="n"/>
+      <c r="AB65" s="10" t="n"/>
+      <c r="AC65" s="10" t="n"/>
+      <c r="AD65" s="11" t="n"/>
+      <c r="AE65" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF65" s="11" t="n"/>
+      <c r="AG65" s="45" t="inlineStr"/>
+      <c r="AH65" s="10" t="n"/>
+      <c r="AI65" s="11" t="n"/>
+      <c r="AJ65" s="45" t="inlineStr"/>
+      <c r="AK65" s="10" t="n"/>
+      <c r="AL65" s="11" t="n"/>
+      <c r="AM65" s="45" t="inlineStr"/>
+      <c r="AN65" s="10" t="n"/>
+      <c r="AO65" s="11" t="n"/>
+      <c r="AP65" s="45" t="inlineStr"/>
+      <c r="AQ65" s="10" t="n"/>
+      <c r="AR65" s="11" t="n"/>
+      <c r="AS65" s="45" t="inlineStr"/>
+      <c r="AT65" s="10" t="n"/>
+      <c r="AU65" s="11" t="n"/>
+      <c r="AV65" s="45" t="inlineStr"/>
+      <c r="AW65" s="10" t="n"/>
+      <c r="AX65" s="11" t="n"/>
+      <c r="AY65" s="45" t="inlineStr"/>
+      <c r="AZ65" s="10" t="n"/>
+      <c r="BA65" s="11" t="n"/>
+      <c r="BB65" s="45" t="inlineStr"/>
+      <c r="BC65" s="10" t="n"/>
+      <c r="BD65" s="11" t="n"/>
+      <c r="BE65" s="45" t="inlineStr"/>
+      <c r="BF65" s="10" t="n"/>
+      <c r="BG65" s="11" t="n"/>
+      <c r="BH65" s="45" t="inlineStr"/>
+      <c r="BI65" s="10" t="n"/>
+      <c r="BJ65" s="11" t="n"/>
+      <c r="BK65" s="46" t="inlineStr"/>
+      <c r="BL65" s="10" t="n"/>
+      <c r="BM65" s="10" t="n"/>
+      <c r="BN65" s="10" t="n"/>
+      <c r="BO65" s="10" t="n"/>
+      <c r="BP65" s="10" t="n"/>
+      <c r="BQ65" s="11" t="n"/>
+    </row>
+    <row r="66" ht="128" customHeight="1">
+      <c r="A66" s="44" t="n">
+        <v>49</v>
+      </c>
+      <c r="B66" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-020-049</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="n"/>
+      <c r="D66" s="11" t="n"/>
+      <c r="E66" s="46" t="inlineStr">
+        <is>
+          <t>プレビュー0件（MSG-020-002）</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="11" t="n"/>
+      <c r="J66" s="46" t="inlineStr">
+        <is>
+          <t>・CHUOKAI でログイン済み
+・指定条件に集計対象が存在しない</t>
+        </is>
+      </c>
+      <c r="K66" s="10" t="n"/>
+      <c r="L66" s="10" t="n"/>
+      <c r="M66" s="10" t="n"/>
+      <c r="N66" s="10" t="n"/>
+      <c r="O66" s="10" t="n"/>
+      <c r="P66" s="11" t="n"/>
+      <c r="Q66" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>対象0件になる条件で「作成開始」を実行する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R66" s="10" t="n"/>
+      <c r="S66" s="10" t="n"/>
+      <c r="T66" s="10" t="n"/>
+      <c r="U66" s="10" t="n"/>
+      <c r="V66" s="10" t="n"/>
+      <c r="W66" s="11" t="n"/>
+      <c r="X66" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・preview が 404（`NO_TARGET_DATA`）を返すこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・画面内に「対象データがありません。」（ACSMS-MSG-020-002）が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・「ファイル作成」ボタンが表示されないこと</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y66" s="10" t="n"/>
+      <c r="Z66" s="10" t="n"/>
+      <c r="AA66" s="10" t="n"/>
+      <c r="AB66" s="10" t="n"/>
+      <c r="AC66" s="10" t="n"/>
+      <c r="AD66" s="11" t="n"/>
+      <c r="AE66" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF66" s="11" t="n"/>
+      <c r="AG66" s="45" t="inlineStr"/>
+      <c r="AH66" s="10" t="n"/>
+      <c r="AI66" s="11" t="n"/>
+      <c r="AJ66" s="45" t="inlineStr"/>
+      <c r="AK66" s="10" t="n"/>
+      <c r="AL66" s="11" t="n"/>
+      <c r="AM66" s="45" t="inlineStr"/>
+      <c r="AN66" s="10" t="n"/>
+      <c r="AO66" s="11" t="n"/>
+      <c r="AP66" s="45" t="inlineStr"/>
+      <c r="AQ66" s="10" t="n"/>
+      <c r="AR66" s="11" t="n"/>
+      <c r="AS66" s="45" t="inlineStr"/>
+      <c r="AT66" s="10" t="n"/>
+      <c r="AU66" s="11" t="n"/>
+      <c r="AV66" s="45" t="inlineStr"/>
+      <c r="AW66" s="10" t="n"/>
+      <c r="AX66" s="11" t="n"/>
+      <c r="AY66" s="45" t="inlineStr"/>
+      <c r="AZ66" s="10" t="n"/>
+      <c r="BA66" s="11" t="n"/>
+      <c r="BB66" s="45" t="inlineStr"/>
+      <c r="BC66" s="10" t="n"/>
+      <c r="BD66" s="11" t="n"/>
+      <c r="BE66" s="45" t="inlineStr"/>
+      <c r="BF66" s="10" t="n"/>
+      <c r="BG66" s="11" t="n"/>
+      <c r="BH66" s="45" t="inlineStr"/>
+      <c r="BI66" s="10" t="n"/>
+      <c r="BJ66" s="11" t="n"/>
+      <c r="BK66" s="46" t="inlineStr"/>
+      <c r="BL66" s="10" t="n"/>
+      <c r="BM66" s="10" t="n"/>
+      <c r="BN66" s="10" t="n"/>
+      <c r="BO66" s="10" t="n"/>
+      <c r="BP66" s="10" t="n"/>
+      <c r="BQ66" s="11" t="n"/>
+    </row>
+    <row r="67" ht="240" customHeight="1">
+      <c r="A67" s="44" t="n">
+        <v>50</v>
+      </c>
+      <c r="B67" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-020-050</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="n"/>
+      <c r="D67" s="11" t="n"/>
+      <c r="E67" s="46" t="inlineStr">
+        <is>
+          <t>金額編集がファイルに反映される</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="n"/>
+      <c r="G67" s="10" t="n"/>
+      <c r="H67" s="10" t="n"/>
+      <c r="I67" s="11" t="n"/>
+      <c r="J67" s="46" t="inlineStr">
+        <is>
+          <t>・作成開始でプレビュー表示済み</t>
+        </is>
+      </c>
+      <c r="K67" s="10" t="n"/>
+      <c r="L67" s="10" t="n"/>
+      <c r="M67" s="10" t="n"/>
+      <c r="N67" s="10" t="n"/>
+      <c r="O67" s="10" t="n"/>
+      <c r="P67" s="11" t="n"/>
+      <c r="Q67" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">プレビュー一覧表で1行目の金額を 4900 → 8000 に編集する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>「ファイル作成」を実行する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R67" s="10" t="n"/>
+      <c r="S67" s="10" t="n"/>
+      <c r="T67" s="10" t="n"/>
+      <c r="U67" s="10" t="n"/>
+      <c r="V67" s="10" t="n"/>
+      <c r="W67" s="11" t="n"/>
+      <c r="X67" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・合計金額が編集に応じて更新されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・POST /export の body に `rows: [{ dokusya_id, furikae_kingaku: 8000 }, ...]` が含まれること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・全銀CSVのデータレコードの引落金額・トレーラーの合計金額が編集値（8000）で出力されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・t_koza_furikae にも編集金額（8000）が保存されること</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y67" s="10" t="n"/>
+      <c r="Z67" s="10" t="n"/>
+      <c r="AA67" s="10" t="n"/>
+      <c r="AB67" s="10" t="n"/>
+      <c r="AC67" s="10" t="n"/>
+      <c r="AD67" s="11" t="n"/>
+      <c r="AE67" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF67" s="11" t="n"/>
+      <c r="AG67" s="45" t="inlineStr"/>
+      <c r="AH67" s="10" t="n"/>
+      <c r="AI67" s="11" t="n"/>
+      <c r="AJ67" s="45" t="inlineStr"/>
+      <c r="AK67" s="10" t="n"/>
+      <c r="AL67" s="11" t="n"/>
+      <c r="AM67" s="45" t="inlineStr"/>
+      <c r="AN67" s="10" t="n"/>
+      <c r="AO67" s="11" t="n"/>
+      <c r="AP67" s="45" t="inlineStr"/>
+      <c r="AQ67" s="10" t="n"/>
+      <c r="AR67" s="11" t="n"/>
+      <c r="AS67" s="45" t="inlineStr"/>
+      <c r="AT67" s="10" t="n"/>
+      <c r="AU67" s="11" t="n"/>
+      <c r="AV67" s="45" t="inlineStr"/>
+      <c r="AW67" s="10" t="n"/>
+      <c r="AX67" s="11" t="n"/>
+      <c r="AY67" s="45" t="inlineStr"/>
+      <c r="AZ67" s="10" t="n"/>
+      <c r="BA67" s="11" t="n"/>
+      <c r="BB67" s="45" t="inlineStr"/>
+      <c r="BC67" s="10" t="n"/>
+      <c r="BD67" s="11" t="n"/>
+      <c r="BE67" s="45" t="inlineStr"/>
+      <c r="BF67" s="10" t="n"/>
+      <c r="BG67" s="11" t="n"/>
+      <c r="BH67" s="45" t="inlineStr"/>
+      <c r="BI67" s="10" t="n"/>
+      <c r="BJ67" s="11" t="n"/>
+      <c r="BK67" s="46" t="inlineStr"/>
+      <c r="BL67" s="10" t="n"/>
+      <c r="BM67" s="10" t="n"/>
+      <c r="BN67" s="10" t="n"/>
+      <c r="BO67" s="10" t="n"/>
+      <c r="BP67" s="10" t="n"/>
+      <c r="BQ67" s="11" t="n"/>
+    </row>
+    <row r="68" ht="192" customHeight="1">
+      <c r="A68" s="44" t="n">
+        <v>51</v>
+      </c>
+      <c r="B68" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-020-051</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="n"/>
+      <c r="D68" s="11" t="n"/>
+      <c r="E68" s="46" t="inlineStr">
+        <is>
+          <t>ファイル作成でダウンロード（拡張子なし ZENOUTFD）</t>
+        </is>
+      </c>
+      <c r="F68" s="10" t="n"/>
+      <c r="G68" s="10" t="n"/>
+      <c r="H68" s="10" t="n"/>
+      <c r="I68" s="11" t="n"/>
+      <c r="J68" s="46" t="inlineStr">
+        <is>
+          <t>・プレビュー表示済み・JASTEM情報が設定済み</t>
+        </is>
+      </c>
+      <c r="K68" s="10" t="n"/>
+      <c r="L68" s="10" t="n"/>
+      <c r="M68" s="10" t="n"/>
+      <c r="N68" s="10" t="n"/>
+      <c r="O68" s="10" t="n"/>
+      <c r="P68" s="11" t="n"/>
+      <c r="Q68" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>「ファイル作成」を実行する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R68" s="10" t="n"/>
+      <c r="S68" s="10" t="n"/>
+      <c r="T68" s="10" t="n"/>
+      <c r="U68" s="10" t="n"/>
+      <c r="V68" s="10" t="n"/>
+      <c r="W68" s="11" t="n"/>
+      <c r="X68" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・全銀フォーマット固定長ファイルがダウンロードされること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・**ダウンロード名が `ZENOUTFD`（拡張子なし・.txt/.csv等が付かない）であること**
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・S3保存名・t_file_download.file_name も拡張子なしであること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・「口座振替データの作成が完了しました。」（ACSMS-MSG-020-001）が表示されること</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y68" s="10" t="n"/>
+      <c r="Z68" s="10" t="n"/>
+      <c r="AA68" s="10" t="n"/>
+      <c r="AB68" s="10" t="n"/>
+      <c r="AC68" s="10" t="n"/>
+      <c r="AD68" s="11" t="n"/>
+      <c r="AE68" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF68" s="11" t="n"/>
+      <c r="AG68" s="45" t="inlineStr"/>
+      <c r="AH68" s="10" t="n"/>
+      <c r="AI68" s="11" t="n"/>
+      <c r="AJ68" s="45" t="inlineStr"/>
+      <c r="AK68" s="10" t="n"/>
+      <c r="AL68" s="11" t="n"/>
+      <c r="AM68" s="45" t="inlineStr"/>
+      <c r="AN68" s="10" t="n"/>
+      <c r="AO68" s="11" t="n"/>
+      <c r="AP68" s="45" t="inlineStr"/>
+      <c r="AQ68" s="10" t="n"/>
+      <c r="AR68" s="11" t="n"/>
+      <c r="AS68" s="45" t="inlineStr"/>
+      <c r="AT68" s="10" t="n"/>
+      <c r="AU68" s="11" t="n"/>
+      <c r="AV68" s="45" t="inlineStr"/>
+      <c r="AW68" s="10" t="n"/>
+      <c r="AX68" s="11" t="n"/>
+      <c r="AY68" s="45" t="inlineStr"/>
+      <c r="AZ68" s="10" t="n"/>
+      <c r="BA68" s="11" t="n"/>
+      <c r="BB68" s="45" t="inlineStr"/>
+      <c r="BC68" s="10" t="n"/>
+      <c r="BD68" s="11" t="n"/>
+      <c r="BE68" s="45" t="inlineStr"/>
+      <c r="BF68" s="10" t="n"/>
+      <c r="BG68" s="11" t="n"/>
+      <c r="BH68" s="45" t="inlineStr"/>
+      <c r="BI68" s="10" t="n"/>
+      <c r="BJ68" s="11" t="n"/>
+      <c r="BK68" s="46" t="inlineStr"/>
+      <c r="BL68" s="10" t="n"/>
+      <c r="BM68" s="10" t="n"/>
+      <c r="BN68" s="10" t="n"/>
+      <c r="BO68" s="10" t="n"/>
+      <c r="BP68" s="10" t="n"/>
+      <c r="BQ68" s="11" t="n"/>
+    </row>
+    <row r="69" ht="160" customHeight="1">
+      <c r="A69" s="44" t="n">
+        <v>52</v>
+      </c>
+      <c r="B69" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-020-052</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="n"/>
+      <c r="D69" s="11" t="n"/>
+      <c r="E69" s="46" t="inlineStr">
+        <is>
+          <t>スコープ外 dokusya_id の拒否（セキュリティ）</t>
+        </is>
+      </c>
+      <c r="F69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
+      <c r="H69" s="10" t="n"/>
+      <c r="I69" s="11" t="n"/>
+      <c r="J69" s="46" t="inlineStr">
+        <is>
+          <t>・CHUOKAI でログイン済み（自JAのみ）</t>
+        </is>
+      </c>
+      <c r="K69" s="10" t="n"/>
+      <c r="L69" s="10" t="n"/>
+      <c r="M69" s="10" t="n"/>
+      <c r="N69" s="10" t="n"/>
+      <c r="O69" s="10" t="n"/>
+      <c r="P69" s="11" t="n"/>
+      <c r="Q69" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>export リクエストの `rows` に、自JAのスコープ外／存在しない `dokusya_id`（例: 999）と巨額金額を混入させて送信する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R69" s="10" t="n"/>
+      <c r="S69" s="10" t="n"/>
+      <c r="T69" s="10" t="n"/>
+      <c r="U69" s="10" t="n"/>
+      <c r="V69" s="10" t="n"/>
+      <c r="W69" s="11" t="n"/>
+      <c r="X69" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・サーバがスコープ再集計した対象と突合し、**スコープ外/不正な dokusya_id は無視されること**
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・出力ファイル・t_koza_furikae に混入した偽IDの行・巨額金額が含まれないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・スコープ内の実在行は正しい金額で出力されること</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y69" s="10" t="n"/>
+      <c r="Z69" s="10" t="n"/>
+      <c r="AA69" s="10" t="n"/>
+      <c r="AB69" s="10" t="n"/>
+      <c r="AC69" s="10" t="n"/>
+      <c r="AD69" s="11" t="n"/>
+      <c r="AE69" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF69" s="11" t="n"/>
+      <c r="AG69" s="45" t="inlineStr"/>
+      <c r="AH69" s="10" t="n"/>
+      <c r="AI69" s="11" t="n"/>
+      <c r="AJ69" s="45" t="inlineStr"/>
+      <c r="AK69" s="10" t="n"/>
+      <c r="AL69" s="11" t="n"/>
+      <c r="AM69" s="45" t="inlineStr"/>
+      <c r="AN69" s="10" t="n"/>
+      <c r="AO69" s="11" t="n"/>
+      <c r="AP69" s="45" t="inlineStr"/>
+      <c r="AQ69" s="10" t="n"/>
+      <c r="AR69" s="11" t="n"/>
+      <c r="AS69" s="45" t="inlineStr"/>
+      <c r="AT69" s="10" t="n"/>
+      <c r="AU69" s="11" t="n"/>
+      <c r="AV69" s="45" t="inlineStr"/>
+      <c r="AW69" s="10" t="n"/>
+      <c r="AX69" s="11" t="n"/>
+      <c r="AY69" s="45" t="inlineStr"/>
+      <c r="AZ69" s="10" t="n"/>
+      <c r="BA69" s="11" t="n"/>
+      <c r="BB69" s="45" t="inlineStr"/>
+      <c r="BC69" s="10" t="n"/>
+      <c r="BD69" s="11" t="n"/>
+      <c r="BE69" s="45" t="inlineStr"/>
+      <c r="BF69" s="10" t="n"/>
+      <c r="BG69" s="11" t="n"/>
+      <c r="BH69" s="45" t="inlineStr"/>
+      <c r="BI69" s="10" t="n"/>
+      <c r="BJ69" s="11" t="n"/>
+      <c r="BK69" s="46" t="inlineStr"/>
+      <c r="BL69" s="10" t="n"/>
+      <c r="BM69" s="10" t="n"/>
+      <c r="BN69" s="10" t="n"/>
+      <c r="BO69" s="10" t="n"/>
+      <c r="BP69" s="10" t="n"/>
+      <c r="BQ69" s="11" t="n"/>
+    </row>
+    <row r="70" ht="112" customHeight="1">
+      <c r="A70" s="44" t="n">
+        <v>53</v>
+      </c>
+      <c r="B70" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-020-053</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="n"/>
+      <c r="D70" s="11" t="n"/>
+      <c r="E70" s="46" t="inlineStr">
+        <is>
+          <t>フィルタ変更でプレビュー破棄</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
+      <c r="H70" s="10" t="n"/>
+      <c r="I70" s="11" t="n"/>
+      <c r="J70" s="46" t="inlineStr">
+        <is>
+          <t>・プレビュー表示済み</t>
+        </is>
+      </c>
+      <c r="K70" s="10" t="n"/>
+      <c r="L70" s="10" t="n"/>
+      <c r="M70" s="10" t="n"/>
+      <c r="N70" s="10" t="n"/>
+      <c r="O70" s="10" t="n"/>
+      <c r="P70" s="11" t="n"/>
+      <c r="Q70" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>プレビュー表示後に、年月日または管理支店／支店／口座支店の絞込を変更する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R70" s="10" t="n"/>
+      <c r="S70" s="10" t="n"/>
+      <c r="T70" s="10" t="n"/>
+      <c r="U70" s="10" t="n"/>
+      <c r="V70" s="10" t="n"/>
+      <c r="W70" s="11" t="n"/>
+      <c r="X70" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・プレビューが破棄され、「ファイル作成」ボタンが非表示になること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・再度「作成開始」を押すまでファイル作成できないこと（古いプレビューで出力させない）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y70" s="10" t="n"/>
+      <c r="Z70" s="10" t="n"/>
+      <c r="AA70" s="10" t="n"/>
+      <c r="AB70" s="10" t="n"/>
+      <c r="AC70" s="10" t="n"/>
+      <c r="AD70" s="11" t="n"/>
+      <c r="AE70" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF70" s="11" t="n"/>
+      <c r="AG70" s="45" t="inlineStr"/>
+      <c r="AH70" s="10" t="n"/>
+      <c r="AI70" s="11" t="n"/>
+      <c r="AJ70" s="45" t="inlineStr"/>
+      <c r="AK70" s="10" t="n"/>
+      <c r="AL70" s="11" t="n"/>
+      <c r="AM70" s="45" t="inlineStr"/>
+      <c r="AN70" s="10" t="n"/>
+      <c r="AO70" s="11" t="n"/>
+      <c r="AP70" s="45" t="inlineStr"/>
+      <c r="AQ70" s="10" t="n"/>
+      <c r="AR70" s="11" t="n"/>
+      <c r="AS70" s="45" t="inlineStr"/>
+      <c r="AT70" s="10" t="n"/>
+      <c r="AU70" s="11" t="n"/>
+      <c r="AV70" s="45" t="inlineStr"/>
+      <c r="AW70" s="10" t="n"/>
+      <c r="AX70" s="11" t="n"/>
+      <c r="AY70" s="45" t="inlineStr"/>
+      <c r="AZ70" s="10" t="n"/>
+      <c r="BA70" s="11" t="n"/>
+      <c r="BB70" s="45" t="inlineStr"/>
+      <c r="BC70" s="10" t="n"/>
+      <c r="BD70" s="11" t="n"/>
+      <c r="BE70" s="45" t="inlineStr"/>
+      <c r="BF70" s="10" t="n"/>
+      <c r="BG70" s="11" t="n"/>
+      <c r="BH70" s="45" t="inlineStr"/>
+      <c r="BI70" s="10" t="n"/>
+      <c r="BJ70" s="11" t="n"/>
+      <c r="BK70" s="46" t="inlineStr"/>
+      <c r="BL70" s="10" t="n"/>
+      <c r="BM70" s="10" t="n"/>
+      <c r="BN70" s="10" t="n"/>
+      <c r="BO70" s="10" t="n"/>
+      <c r="BP70" s="10" t="n"/>
+      <c r="BQ70" s="11" t="n"/>
+    </row>
+    <row r="71" ht="128" customHeight="1">
+      <c r="A71" s="44" t="n">
+        <v>54</v>
+      </c>
+      <c r="B71" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-020-054</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="n"/>
+      <c r="D71" s="11" t="n"/>
+      <c r="E71" s="46" t="inlineStr">
+        <is>
+          <t>JASTEM未設定エラーで出力不可</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="n"/>
+      <c r="G71" s="10" t="n"/>
+      <c r="H71" s="10" t="n"/>
+      <c r="I71" s="11" t="n"/>
+      <c r="J71" s="46" t="inlineStr">
+        <is>
+          <t>・プレビュー表示済み
+・JASTEM情報（委託者/農協/店舗/口座）が未設定（口座支店未選択やマスタ未登録）</t>
+        </is>
+      </c>
+      <c r="K71" s="10" t="n"/>
+      <c r="L71" s="10" t="n"/>
+      <c r="M71" s="10" t="n"/>
+      <c r="N71" s="10" t="n"/>
+      <c r="O71" s="10" t="n"/>
+      <c r="P71" s="11" t="n"/>
+      <c r="Q71" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>JASTEM情報が未設定の状態で「ファイル作成」を実行する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R71" s="10" t="n"/>
+      <c r="S71" s="10" t="n"/>
+      <c r="T71" s="10" t="n"/>
+      <c r="U71" s="10" t="n"/>
+      <c r="V71" s="10" t="n"/>
+      <c r="W71" s="11" t="n"/>
+      <c r="X71" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・「JASTEM委託者情報・金融機関支店情報が未設定のため出力できません。…」のエラーが表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・POST /export が呼ばれず、ファイルがダウンロードされないこと</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y71" s="10" t="n"/>
+      <c r="Z71" s="10" t="n"/>
+      <c r="AA71" s="10" t="n"/>
+      <c r="AB71" s="10" t="n"/>
+      <c r="AC71" s="10" t="n"/>
+      <c r="AD71" s="11" t="n"/>
+      <c r="AE71" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF71" s="11" t="n"/>
+      <c r="AG71" s="45" t="inlineStr"/>
+      <c r="AH71" s="10" t="n"/>
+      <c r="AI71" s="11" t="n"/>
+      <c r="AJ71" s="45" t="inlineStr"/>
+      <c r="AK71" s="10" t="n"/>
+      <c r="AL71" s="11" t="n"/>
+      <c r="AM71" s="45" t="inlineStr"/>
+      <c r="AN71" s="10" t="n"/>
+      <c r="AO71" s="11" t="n"/>
+      <c r="AP71" s="45" t="inlineStr"/>
+      <c r="AQ71" s="10" t="n"/>
+      <c r="AR71" s="11" t="n"/>
+      <c r="AS71" s="45" t="inlineStr"/>
+      <c r="AT71" s="10" t="n"/>
+      <c r="AU71" s="11" t="n"/>
+      <c r="AV71" s="45" t="inlineStr"/>
+      <c r="AW71" s="10" t="n"/>
+      <c r="AX71" s="11" t="n"/>
+      <c r="AY71" s="45" t="inlineStr"/>
+      <c r="AZ71" s="10" t="n"/>
+      <c r="BA71" s="11" t="n"/>
+      <c r="BB71" s="45" t="inlineStr"/>
+      <c r="BC71" s="10" t="n"/>
+      <c r="BD71" s="11" t="n"/>
+      <c r="BE71" s="45" t="inlineStr"/>
+      <c r="BF71" s="10" t="n"/>
+      <c r="BG71" s="11" t="n"/>
+      <c r="BH71" s="45" t="inlineStr"/>
+      <c r="BI71" s="10" t="n"/>
+      <c r="BJ71" s="11" t="n"/>
+      <c r="BK71" s="46" t="inlineStr"/>
+      <c r="BL71" s="10" t="n"/>
+      <c r="BM71" s="10" t="n"/>
+      <c r="BN71" s="10" t="n"/>
+      <c r="BO71" s="10" t="n"/>
+      <c r="BP71" s="10" t="n"/>
+      <c r="BQ71" s="11" t="n"/>
+    </row>
+    <row r="72" ht="112" customHeight="1">
+      <c r="A72" s="44" t="n">
+        <v>55</v>
+      </c>
+      <c r="B72" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-020-055</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="n"/>
+      <c r="D72" s="11" t="n"/>
+      <c r="E72" s="46" t="inlineStr">
+        <is>
+          <t>金額の範囲チェック（0〜10桁）</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
+      <c r="H72" s="10" t="n"/>
+      <c r="I72" s="11" t="n"/>
+      <c r="J72" s="46" t="inlineStr">
+        <is>
+          <t>・プレビュー表示済み</t>
+        </is>
+      </c>
+      <c r="K72" s="10" t="n"/>
+      <c r="L72" s="10" t="n"/>
+      <c r="M72" s="10" t="n"/>
+      <c r="N72" s="10" t="n"/>
+      <c r="O72" s="10" t="n"/>
+      <c r="P72" s="11" t="n"/>
+      <c r="Q72" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>金額に負数（例: -5）または10桁超（例: 10,000,000,000）を入力して「ファイル作成」を実行する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R72" s="10" t="n"/>
+      <c r="S72" s="10" t="n"/>
+      <c r="T72" s="10" t="n"/>
+      <c r="U72" s="10" t="n"/>
+      <c r="V72" s="10" t="n"/>
+      <c r="W72" s="11" t="n"/>
+      <c r="X72" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・金額範囲エラーが表示され、POST /export が呼ばれないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・（FEの a-input-number でも 0〜9,999,999,999 に制約されること）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y72" s="10" t="n"/>
+      <c r="Z72" s="10" t="n"/>
+      <c r="AA72" s="10" t="n"/>
+      <c r="AB72" s="10" t="n"/>
+      <c r="AC72" s="10" t="n"/>
+      <c r="AD72" s="11" t="n"/>
+      <c r="AE72" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF72" s="11" t="n"/>
+      <c r="AG72" s="45" t="inlineStr"/>
+      <c r="AH72" s="10" t="n"/>
+      <c r="AI72" s="11" t="n"/>
+      <c r="AJ72" s="45" t="inlineStr"/>
+      <c r="AK72" s="10" t="n"/>
+      <c r="AL72" s="11" t="n"/>
+      <c r="AM72" s="45" t="inlineStr"/>
+      <c r="AN72" s="10" t="n"/>
+      <c r="AO72" s="11" t="n"/>
+      <c r="AP72" s="45" t="inlineStr"/>
+      <c r="AQ72" s="10" t="n"/>
+      <c r="AR72" s="11" t="n"/>
+      <c r="AS72" s="45" t="inlineStr"/>
+      <c r="AT72" s="10" t="n"/>
+      <c r="AU72" s="11" t="n"/>
+      <c r="AV72" s="45" t="inlineStr"/>
+      <c r="AW72" s="10" t="n"/>
+      <c r="AX72" s="11" t="n"/>
+      <c r="AY72" s="45" t="inlineStr"/>
+      <c r="AZ72" s="10" t="n"/>
+      <c r="BA72" s="11" t="n"/>
+      <c r="BB72" s="45" t="inlineStr"/>
+      <c r="BC72" s="10" t="n"/>
+      <c r="BD72" s="11" t="n"/>
+      <c r="BE72" s="45" t="inlineStr"/>
+      <c r="BF72" s="10" t="n"/>
+      <c r="BG72" s="11" t="n"/>
+      <c r="BH72" s="45" t="inlineStr"/>
+      <c r="BI72" s="10" t="n"/>
+      <c r="BJ72" s="11" t="n"/>
+      <c r="BK72" s="46" t="inlineStr"/>
+      <c r="BL72" s="10" t="n"/>
+      <c r="BM72" s="10" t="n"/>
+      <c r="BN72" s="10" t="n"/>
+      <c r="BO72" s="10" t="n"/>
+      <c r="BP72" s="10" t="n"/>
+      <c r="BQ72" s="11" t="n"/>
+    </row>
+    <row r="73" ht="22.5" customHeight="1">
+      <c r="A73" s="32" t="inlineStr">
+        <is>
+          <t>カテゴリ7: 集計対象の限定・出力ブロック（Scope / Export Gate）</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="n"/>
+      <c r="C73" s="10" t="n"/>
+      <c r="D73" s="10" t="n"/>
+      <c r="E73" s="10" t="n"/>
+      <c r="F73" s="10" t="n"/>
+      <c r="G73" s="10" t="n"/>
+      <c r="H73" s="10" t="n"/>
+      <c r="I73" s="10" t="n"/>
+      <c r="J73" s="10" t="n"/>
+      <c r="K73" s="10" t="n"/>
+      <c r="L73" s="10" t="n"/>
+      <c r="M73" s="10" t="n"/>
+      <c r="N73" s="10" t="n"/>
+      <c r="O73" s="10" t="n"/>
+      <c r="P73" s="10" t="n"/>
+      <c r="Q73" s="10" t="n"/>
+      <c r="R73" s="10" t="n"/>
+      <c r="S73" s="10" t="n"/>
+      <c r="T73" s="10" t="n"/>
+      <c r="U73" s="10" t="n"/>
+      <c r="V73" s="10" t="n"/>
+      <c r="W73" s="10" t="n"/>
+      <c r="X73" s="10" t="n"/>
+      <c r="Y73" s="10" t="n"/>
+      <c r="Z73" s="10" t="n"/>
+      <c r="AA73" s="10" t="n"/>
+      <c r="AB73" s="10" t="n"/>
+      <c r="AC73" s="10" t="n"/>
+      <c r="AD73" s="10" t="n"/>
+      <c r="AE73" s="10" t="n"/>
+      <c r="AF73" s="10" t="n"/>
+      <c r="AG73" s="10" t="n"/>
+      <c r="AH73" s="10" t="n"/>
+      <c r="AI73" s="10" t="n"/>
+      <c r="AJ73" s="10" t="n"/>
+      <c r="AK73" s="10" t="n"/>
+      <c r="AL73" s="10" t="n"/>
+      <c r="AM73" s="10" t="n"/>
+      <c r="AN73" s="10" t="n"/>
+      <c r="AO73" s="10" t="n"/>
+      <c r="AP73" s="10" t="n"/>
+      <c r="AQ73" s="10" t="n"/>
+      <c r="AR73" s="10" t="n"/>
+      <c r="AS73" s="10" t="n"/>
+      <c r="AT73" s="10" t="n"/>
+      <c r="AU73" s="10" t="n"/>
+      <c r="AV73" s="10" t="n"/>
+      <c r="AW73" s="10" t="n"/>
+      <c r="AX73" s="10" t="n"/>
+      <c r="AY73" s="10" t="n"/>
+      <c r="AZ73" s="10" t="n"/>
+      <c r="BA73" s="10" t="n"/>
+      <c r="BB73" s="10" t="n"/>
+      <c r="BC73" s="10" t="n"/>
+      <c r="BD73" s="10" t="n"/>
+      <c r="BE73" s="10" t="n"/>
+      <c r="BF73" s="10" t="n"/>
+      <c r="BG73" s="10" t="n"/>
+      <c r="BH73" s="10" t="n"/>
+      <c r="BI73" s="10" t="n"/>
+      <c r="BJ73" s="10" t="n"/>
+      <c r="BK73" s="10" t="n"/>
+      <c r="BL73" s="10" t="n"/>
+      <c r="BM73" s="10" t="n"/>
+      <c r="BN73" s="10" t="n"/>
+      <c r="BO73" s="10" t="n"/>
+      <c r="BP73" s="10" t="n"/>
+      <c r="BQ73" s="11" t="n"/>
+    </row>
+    <row r="74" ht="450" customHeight="1">
+      <c r="A74" s="44" t="n">
+        <v>56</v>
+      </c>
+      <c r="B74" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-020-056</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="n"/>
+      <c r="D74" s="11" t="n"/>
+      <c r="E74" s="46" t="inlineStr">
+        <is>
+          <t>集計対象 — 購読種別による限定（紙版と承認済・有料の電子版のみ／#56600）</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="n"/>
+      <c r="G74" s="10" t="n"/>
+      <c r="H74" s="10" t="n"/>
+      <c r="I74" s="11" t="n"/>
+      <c r="J74" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（`koza_furikae.export` 権限あり）
+・支払方法=口座引落・手続種類=新規（継続）・出力対象年月に購読中の購読者が以下のとおり存在すること
+・(a) 紙版（dokusya_shubetsu=1）2件
+・(b) 電子版（2）・承認済（denshi_shonin_status=1）・有料（denshi_dokusya_shubetsu=1）2件
+・(c) 電子版（2）・**未承認**（denshi_shonin_status=0）・有料 1件
+・(d) 電子版（2）・承認済・**無料**（denshi_dokusya_shubetsu=0）1件
+・(e) 電子版（2）・**否認**（denshi_shonin_status=2）・有料 1件
+・(f) 併読（dokusya_shubetsu=3）1件</t>
+        </is>
+      </c>
+      <c r="K74" s="10" t="n"/>
+      <c r="L74" s="10" t="n"/>
+      <c r="M74" s="10" t="n"/>
+      <c r="N74" s="10" t="n"/>
+      <c r="O74" s="10" t="n"/>
+      <c r="P74" s="11" t="n"/>
+      <c r="Q74" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">出力対象年月を指定して「作成開始」をクリックし、プレビュー一覧の件数と明細を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ファイルを作成し、データレコードの件数と合計金額を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">(f) 併読の購読者がプレビュー・ファイルの双方に含まれないことを確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">(a) 紙版1件と (d) 無料電子版1件だけが残る条件（管理支店で絞る等）で出力し、対象が紙版1件のみになることを確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(c)(d)(e)(f) のいずれかが**失効した単価**を参照している状態にして出力する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R74" s="10" t="n"/>
+      <c r="S74" s="10" t="n"/>
+      <c r="T74" s="10" t="n"/>
+      <c r="U74" s="10" t="n"/>
+      <c r="V74" s="10" t="n"/>
+      <c r="W74" s="11" t="n"/>
+      <c r="X74" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">(a) 2件と (b) 2件の**計4件のみ**が表示されること。(c)(d)(e)(f) は表示されないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">データレコードが4件であること。合計金額が対象4件の合計と一致すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">併読は集計対象外であること（従来は購読種別で絞っておらず、併読も口座引落の対象になり得た）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">紙版1件のみが対象となること（無料の電子版は購読料が発生しないため引き落とす対象が無い）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">出力が**ブロックされないこと**（INACTIVE_TANKA_REFERENCED が発生しないこと）。集計対象外の購読者が参照する失効単価は出力可否に影響しない
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・電子版は「承認済かつ有料」の2条件を**両方**満たす場合のみ対象。未承認・否認・無料はいずれも除外（顧客要件2026-08 / #56600）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・ステップ5は集計SQLと失効単価チェックSQLの**両方**に同じ購読種別条件が入っていることの確認。片方だけだと「引落対象ではない購読者が参照する失効単価でエラーになり出力できない」という不整合が起きる
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・同じ限定は増減連絡票（SCR-028）・増減通知（SCR-029）とは別基準のため、本画面の条件をそのまま流用しないこと</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y74" s="10" t="n"/>
+      <c r="Z74" s="10" t="n"/>
+      <c r="AA74" s="10" t="n"/>
+      <c r="AB74" s="10" t="n"/>
+      <c r="AC74" s="10" t="n"/>
+      <c r="AD74" s="11" t="n"/>
+      <c r="AE74" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF74" s="11" t="n"/>
+      <c r="AG74" s="45" t="inlineStr"/>
+      <c r="AH74" s="10" t="n"/>
+      <c r="AI74" s="11" t="n"/>
+      <c r="AJ74" s="45" t="inlineStr"/>
+      <c r="AK74" s="10" t="n"/>
+      <c r="AL74" s="11" t="n"/>
+      <c r="AM74" s="45" t="inlineStr"/>
+      <c r="AN74" s="10" t="n"/>
+      <c r="AO74" s="11" t="n"/>
+      <c r="AP74" s="45" t="inlineStr"/>
+      <c r="AQ74" s="10" t="n"/>
+      <c r="AR74" s="11" t="n"/>
+      <c r="AS74" s="45" t="inlineStr"/>
+      <c r="AT74" s="10" t="n"/>
+      <c r="AU74" s="11" t="n"/>
+      <c r="AV74" s="45" t="inlineStr"/>
+      <c r="AW74" s="10" t="n"/>
+      <c r="AX74" s="11" t="n"/>
+      <c r="AY74" s="45" t="inlineStr"/>
+      <c r="AZ74" s="10" t="n"/>
+      <c r="BA74" s="11" t="n"/>
+      <c r="BB74" s="45" t="inlineStr"/>
+      <c r="BC74" s="10" t="n"/>
+      <c r="BD74" s="11" t="n"/>
+      <c r="BE74" s="45" t="inlineStr"/>
+      <c r="BF74" s="10" t="n"/>
+      <c r="BG74" s="11" t="n"/>
+      <c r="BH74" s="45" t="inlineStr"/>
+      <c r="BI74" s="10" t="n"/>
+      <c r="BJ74" s="11" t="n"/>
+      <c r="BK74" s="46" t="inlineStr"/>
+      <c r="BL74" s="10" t="n"/>
+      <c r="BM74" s="10" t="n"/>
+      <c r="BN74" s="10" t="n"/>
+      <c r="BO74" s="10" t="n"/>
+      <c r="BP74" s="10" t="n"/>
+      <c r="BQ74" s="11" t="n"/>
+    </row>
+    <row r="75" ht="450" customHeight="1">
+      <c r="A75" s="44" t="n">
+        <v>57</v>
+      </c>
+      <c r="B75" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-020-057</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="n"/>
+      <c r="D75" s="11" t="n"/>
+      <c r="E75" s="46" t="inlineStr">
+        <is>
+          <t>出力ブロック — 失効単価を参照する購読者が存在する場合（INACTIVE_TANKA_REFERENCED）</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="n"/>
+      <c r="G75" s="10" t="n"/>
+      <c r="H75" s="10" t="n"/>
+      <c r="I75" s="11" t="n"/>
+      <c r="J75" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（`koza_furikae.export` 権限あり）
+・出力対象の母集合に、`active_flg = FALSE` の単価を参照する購読者が 1 件以上存在すること
+・別途、該当が 20 件以上になるパターンも用意すること（打ち切り確認用）</t>
+        </is>
+      </c>
+      <c r="K75" s="10" t="n"/>
+      <c r="L75" s="10" t="n"/>
+      <c r="M75" s="10" t="n"/>
+      <c r="N75" s="10" t="n"/>
+      <c r="O75" s="10" t="n"/>
+      <c r="P75" s="11" t="n"/>
+      <c r="Q75" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">失効単価を参照する購読者が1件だけ存在する状態で「作成開始」をクリックする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">レスポンスの `error_code`・`message`・`errors[]`・`total` を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">該当が20件存在する状態で同じ操作を行い、`errors[]` の件数と `total` を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">画面のメッセージ表示と誘導先を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">該当購読者の単価を有効な単価へ変更してから再度「作成開始」をクリックする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>単価の適用期間（tekiyo_start / tekiyo_end）が出力対象年月から外れているが `active_flg = TRUE` の単価を参照する購読者で出力する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R75" s="10" t="n"/>
+      <c r="S75" s="10" t="n"/>
+      <c r="T75" s="10" t="n"/>
+      <c r="U75" s="10" t="n"/>
+      <c r="V75" s="10" t="n"/>
+      <c r="W75" s="11" t="n"/>
+      <c r="X75" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">出力がブロックされ、HTTPステータスコード409が返ること。ファイルは生成されないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`error_code: INACTIVE_TANKA_REFERENCED`、`message` が `失効した単価を参照している購読者が存在するため、口座振替データを出力できません。該当購読者の単価を変更してから再度実行してください。` であること。`errors[]` の各要素が `{ field: "&lt;行番号&gt;", message: "&lt;口座名義&gt;（単価: &lt;単価コード&gt; &lt;単価名&gt;）" }` の形であること。`total` が総該当件数であること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`errors[]` が**先頭15件で打ち切られる**こと。`total` は 20 のままであること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「該当 20 件中 15 件を表示」と要約されること。全件の確認・単価変更は**購読者明細検索画面（「失効単価参照」絞込）**へ誘導されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">出力が成功すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">出力が成功すること（有効判定は `active_flg` のみで行い、適用期間の日付判定はしない）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・大量該当（同一失効単価を多数の購読者が参照）でレスポンス・DOMが肥大するのを避けるための打ち切り仕様
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・単価の有効判定を `active_flg` のみにしたのは、単価失効バッチの運用に合わせるため（API設計書 v1.1）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・集計対象外の購読者（#56600 で除外される併読・未承認/無料の電子版）はこのチェックの母集合にも含まれない（ACSMS-TC-020-056 ステップ5 参照）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y75" s="10" t="n"/>
+      <c r="Z75" s="10" t="n"/>
+      <c r="AA75" s="10" t="n"/>
+      <c r="AB75" s="10" t="n"/>
+      <c r="AC75" s="10" t="n"/>
+      <c r="AD75" s="11" t="n"/>
+      <c r="AE75" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF75" s="11" t="n"/>
+      <c r="AG75" s="45" t="inlineStr"/>
+      <c r="AH75" s="10" t="n"/>
+      <c r="AI75" s="11" t="n"/>
+      <c r="AJ75" s="45" t="inlineStr"/>
+      <c r="AK75" s="10" t="n"/>
+      <c r="AL75" s="11" t="n"/>
+      <c r="AM75" s="45" t="inlineStr"/>
+      <c r="AN75" s="10" t="n"/>
+      <c r="AO75" s="11" t="n"/>
+      <c r="AP75" s="45" t="inlineStr"/>
+      <c r="AQ75" s="10" t="n"/>
+      <c r="AR75" s="11" t="n"/>
+      <c r="AS75" s="45" t="inlineStr"/>
+      <c r="AT75" s="10" t="n"/>
+      <c r="AU75" s="11" t="n"/>
+      <c r="AV75" s="45" t="inlineStr"/>
+      <c r="AW75" s="10" t="n"/>
+      <c r="AX75" s="11" t="n"/>
+      <c r="AY75" s="45" t="inlineStr"/>
+      <c r="AZ75" s="10" t="n"/>
+      <c r="BA75" s="11" t="n"/>
+      <c r="BB75" s="45" t="inlineStr"/>
+      <c r="BC75" s="10" t="n"/>
+      <c r="BD75" s="11" t="n"/>
+      <c r="BE75" s="45" t="inlineStr"/>
+      <c r="BF75" s="10" t="n"/>
+      <c r="BG75" s="11" t="n"/>
+      <c r="BH75" s="45" t="inlineStr"/>
+      <c r="BI75" s="10" t="n"/>
+      <c r="BJ75" s="11" t="n"/>
+      <c r="BK75" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL75" s="10" t="n"/>
+      <c r="BM75" s="10" t="n"/>
+      <c r="BN75" s="10" t="n"/>
+      <c r="BO75" s="10" t="n"/>
+      <c r="BP75" s="10" t="n"/>
+      <c r="BQ75" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="870">
+  <mergeCells count="1042">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="B60:D60"/>
@@ -15658,46 +17737,60 @@
     <mergeCell ref="W8:Y8"/>
     <mergeCell ref="Q37:W37"/>
     <mergeCell ref="AJ20:AL20"/>
+    <mergeCell ref="AM65:AO65"/>
     <mergeCell ref="AG24:AI24"/>
     <mergeCell ref="BH39:BJ39"/>
     <mergeCell ref="J57:P57"/>
     <mergeCell ref="W2:AH2"/>
     <mergeCell ref="X10:AD11"/>
+    <mergeCell ref="BK70:BQ70"/>
     <mergeCell ref="AJ22:AL22"/>
+    <mergeCell ref="AY74:BA74"/>
     <mergeCell ref="AG26:AI26"/>
     <mergeCell ref="AP13:AR13"/>
+    <mergeCell ref="AS74:AU74"/>
+    <mergeCell ref="AV75:AX75"/>
     <mergeCell ref="Q38:W38"/>
     <mergeCell ref="AE34:AF34"/>
     <mergeCell ref="AJ51:AL51"/>
+    <mergeCell ref="AP71:AR71"/>
     <mergeCell ref="BK47:BQ47"/>
     <mergeCell ref="E25:I25"/>
+    <mergeCell ref="X74:AD74"/>
+    <mergeCell ref="X68:AD68"/>
     <mergeCell ref="Q40:W40"/>
     <mergeCell ref="AE36:AF36"/>
     <mergeCell ref="AS51:AU51"/>
     <mergeCell ref="Q15:W15"/>
     <mergeCell ref="AV39:AX39"/>
+    <mergeCell ref="AV70:AX70"/>
     <mergeCell ref="E58:I58"/>
     <mergeCell ref="BE20:BG20"/>
     <mergeCell ref="AM34:AO34"/>
     <mergeCell ref="AJ38:AL38"/>
+    <mergeCell ref="J75:P75"/>
     <mergeCell ref="BE35:BG35"/>
     <mergeCell ref="BK48:BQ48"/>
     <mergeCell ref="AM49:AO49"/>
     <mergeCell ref="AE50:AF50"/>
     <mergeCell ref="AG52:AI52"/>
+    <mergeCell ref="X69:AD69"/>
     <mergeCell ref="BE22:BG22"/>
     <mergeCell ref="BH23:BJ23"/>
     <mergeCell ref="BB26:BD26"/>
     <mergeCell ref="AE31:AF31"/>
     <mergeCell ref="H7:J7"/>
     <mergeCell ref="AG45:AI45"/>
+    <mergeCell ref="AS67:AU67"/>
     <mergeCell ref="AY29:BA29"/>
     <mergeCell ref="E20:I20"/>
     <mergeCell ref="AJ33:AL33"/>
     <mergeCell ref="AG37:AI37"/>
     <mergeCell ref="J39:P39"/>
     <mergeCell ref="AE62:AF62"/>
+    <mergeCell ref="B74:D74"/>
     <mergeCell ref="AG47:AI47"/>
+    <mergeCell ref="B68:D68"/>
     <mergeCell ref="AF8:AH8"/>
     <mergeCell ref="BB27:BD27"/>
     <mergeCell ref="AY31:BA31"/>
@@ -15708,21 +17801,27 @@
     <mergeCell ref="BE38:BG38"/>
     <mergeCell ref="AS62:AU62"/>
     <mergeCell ref="AV63:AX63"/>
+    <mergeCell ref="AP66:AR66"/>
     <mergeCell ref="BH49:BJ49"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="AP53:AR53"/>
     <mergeCell ref="X16:AD16"/>
     <mergeCell ref="AE57:AF57"/>
+    <mergeCell ref="BK66:BQ66"/>
     <mergeCell ref="BK53:BQ53"/>
     <mergeCell ref="BH60:BJ60"/>
     <mergeCell ref="AC7:AE7"/>
     <mergeCell ref="AY26:BA26"/>
     <mergeCell ref="BE15:BG15"/>
+    <mergeCell ref="AP68:AR68"/>
+    <mergeCell ref="Q72:W72"/>
+    <mergeCell ref="J65:P65"/>
     <mergeCell ref="AG63:AI63"/>
     <mergeCell ref="X18:AD18"/>
     <mergeCell ref="BE33:BG33"/>
     <mergeCell ref="BB37:BD37"/>
     <mergeCell ref="AG50:AI50"/>
+    <mergeCell ref="AP67:AR67"/>
     <mergeCell ref="BK13:BQ13"/>
     <mergeCell ref="AY57:BA57"/>
     <mergeCell ref="AM58:AO58"/>
@@ -15731,6 +17830,7 @@
     <mergeCell ref="J25:P25"/>
     <mergeCell ref="Q46:W46"/>
     <mergeCell ref="AM24:AO24"/>
+    <mergeCell ref="AJ72:AL72"/>
     <mergeCell ref="AG27:AI27"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="AM60:AO60"/>
@@ -15740,6 +17840,7 @@
     <mergeCell ref="W3:AH3"/>
     <mergeCell ref="E33:I33"/>
     <mergeCell ref="Q48:W48"/>
+    <mergeCell ref="AE75:AF75"/>
     <mergeCell ref="AV13:AX13"/>
     <mergeCell ref="AS17:AU17"/>
     <mergeCell ref="AS11:AU11"/>
@@ -15752,11 +17853,13 @@
     <mergeCell ref="BH44:BJ44"/>
     <mergeCell ref="AS19:AU19"/>
     <mergeCell ref="Q56:W56"/>
+    <mergeCell ref="AS75:AU75"/>
     <mergeCell ref="AE52:AF52"/>
     <mergeCell ref="Q43:W43"/>
     <mergeCell ref="J14:P14"/>
     <mergeCell ref="AE39:AF39"/>
     <mergeCell ref="B51:D51"/>
+    <mergeCell ref="E74:I74"/>
     <mergeCell ref="AM50:AO50"/>
     <mergeCell ref="AJ54:AL54"/>
     <mergeCell ref="AM15:AO15"/>
@@ -15776,6 +17879,7 @@
     <mergeCell ref="AG38:AI38"/>
     <mergeCell ref="BE30:BG30"/>
     <mergeCell ref="AJ43:AL43"/>
+    <mergeCell ref="AY70:BA70"/>
     <mergeCell ref="AV25:AX25"/>
     <mergeCell ref="W6:Y6"/>
     <mergeCell ref="BE29:BG29"/>
@@ -15786,45 +17890,63 @@
     <mergeCell ref="AG40:AI40"/>
     <mergeCell ref="X24:AD24"/>
     <mergeCell ref="BB43:BD43"/>
+    <mergeCell ref="BK68:BQ68"/>
     <mergeCell ref="AY47:BA47"/>
+    <mergeCell ref="AS72:AU72"/>
     <mergeCell ref="BH50:BJ50"/>
     <mergeCell ref="Q36:W36"/>
     <mergeCell ref="BE54:BG54"/>
+    <mergeCell ref="AJ67:AL67"/>
     <mergeCell ref="Q30:W30"/>
+    <mergeCell ref="BK67:BQ67"/>
     <mergeCell ref="AE63:AF63"/>
     <mergeCell ref="X26:AD26"/>
     <mergeCell ref="W1:AH1"/>
     <mergeCell ref="AC8:AE8"/>
+    <mergeCell ref="AP69:AR69"/>
     <mergeCell ref="AP44:AR44"/>
     <mergeCell ref="E23:I23"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="BE56:BG56"/>
+    <mergeCell ref="AJ69:AL69"/>
+    <mergeCell ref="BK69:BQ69"/>
+    <mergeCell ref="AM70:AO70"/>
+    <mergeCell ref="AE71:AF71"/>
     <mergeCell ref="BE43:BG43"/>
     <mergeCell ref="J33:P33"/>
     <mergeCell ref="AE58:AF58"/>
+    <mergeCell ref="AV68:AX68"/>
     <mergeCell ref="BB59:BD59"/>
     <mergeCell ref="AM63:AO63"/>
     <mergeCell ref="X27:AD27"/>
+    <mergeCell ref="AG66:AI66"/>
     <mergeCell ref="BB46:BD46"/>
+    <mergeCell ref="AM74:AO74"/>
     <mergeCell ref="BE57:BG57"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="AY60:BA60"/>
     <mergeCell ref="BB61:BD61"/>
+    <mergeCell ref="AG74:AI74"/>
     <mergeCell ref="AV15:AX15"/>
     <mergeCell ref="AY16:BA16"/>
     <mergeCell ref="Q62:W62"/>
     <mergeCell ref="E34:I34"/>
     <mergeCell ref="BB48:BD48"/>
+    <mergeCell ref="AG68:AI68"/>
     <mergeCell ref="AG43:AI43"/>
+    <mergeCell ref="AP72:AR72"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="E49:I49"/>
+    <mergeCell ref="J68:P68"/>
     <mergeCell ref="AY18:BA18"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="AY45:BA45"/>
     <mergeCell ref="E36:I36"/>
     <mergeCell ref="Q51:W51"/>
+    <mergeCell ref="BH70:BJ70"/>
     <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AV65:AX65"/>
     <mergeCell ref="BH45:BJ45"/>
     <mergeCell ref="AS20:AU20"/>
     <mergeCell ref="AP24:AR24"/>
@@ -15835,8 +17957,10 @@
     <mergeCell ref="BH47:BJ47"/>
     <mergeCell ref="AS22:AU22"/>
     <mergeCell ref="X20:AD20"/>
+    <mergeCell ref="BH72:BJ72"/>
     <mergeCell ref="AP26:AR26"/>
     <mergeCell ref="X14:AD14"/>
+    <mergeCell ref="BH74:BJ74"/>
     <mergeCell ref="X38:AD38"/>
     <mergeCell ref="BH46:BJ46"/>
     <mergeCell ref="BE50:BG50"/>
@@ -15855,12 +17979,14 @@
     <mergeCell ref="AV34:AX34"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="BH58:BJ58"/>
+    <mergeCell ref="Q75:W75"/>
     <mergeCell ref="BK44:BQ44"/>
     <mergeCell ref="AY48:BA48"/>
     <mergeCell ref="BB49:BD49"/>
     <mergeCell ref="AG62:AI62"/>
     <mergeCell ref="AE33:AF33"/>
     <mergeCell ref="BB36:BD36"/>
+    <mergeCell ref="AV74:AX74"/>
     <mergeCell ref="X40:AD40"/>
     <mergeCell ref="E31:I31"/>
     <mergeCell ref="AV36:AX36"/>
@@ -15870,18 +17996,26 @@
     <mergeCell ref="Q52:W52"/>
     <mergeCell ref="Q39:W39"/>
     <mergeCell ref="AS33:AU33"/>
+    <mergeCell ref="AJ75:AL75"/>
     <mergeCell ref="AM36:AO36"/>
     <mergeCell ref="F1:Q1"/>
     <mergeCell ref="AP37:AR37"/>
     <mergeCell ref="J34:P34"/>
     <mergeCell ref="E26:I26"/>
     <mergeCell ref="AY37:BA37"/>
+    <mergeCell ref="BE65:BG65"/>
+    <mergeCell ref="BK72:BQ72"/>
     <mergeCell ref="AS35:AU35"/>
     <mergeCell ref="J49:P49"/>
+    <mergeCell ref="J74:P74"/>
+    <mergeCell ref="AE68:AF68"/>
+    <mergeCell ref="AE74:AF74"/>
     <mergeCell ref="J36:P36"/>
     <mergeCell ref="BB62:BD62"/>
     <mergeCell ref="AJ14:AL14"/>
     <mergeCell ref="AY17:BA17"/>
+    <mergeCell ref="AY66:BA66"/>
+    <mergeCell ref="AJ70:AL70"/>
     <mergeCell ref="AY53:BA53"/>
     <mergeCell ref="BK24:BQ24"/>
     <mergeCell ref="X45:AD45"/>
@@ -15890,9 +18024,14 @@
     <mergeCell ref="BH53:BJ53"/>
     <mergeCell ref="AV29:AX29"/>
     <mergeCell ref="A8:G8"/>
+    <mergeCell ref="Q65:W65"/>
     <mergeCell ref="AV23:AX23"/>
     <mergeCell ref="BB51:BD51"/>
     <mergeCell ref="AP63:AR63"/>
+    <mergeCell ref="AY68:BA68"/>
+    <mergeCell ref="BH71:BJ71"/>
+    <mergeCell ref="BE75:BG75"/>
+    <mergeCell ref="AG75:AI75"/>
     <mergeCell ref="X59:AD59"/>
     <mergeCell ref="K8:M8"/>
     <mergeCell ref="E44:I44"/>
@@ -15901,11 +18040,13 @@
     <mergeCell ref="BH48:BJ48"/>
     <mergeCell ref="AV24:AX24"/>
     <mergeCell ref="BE58:BG58"/>
+    <mergeCell ref="AJ65:AL65"/>
     <mergeCell ref="T8:V8"/>
     <mergeCell ref="AP27:AR27"/>
     <mergeCell ref="AM31:AO31"/>
     <mergeCell ref="BE39:BG39"/>
     <mergeCell ref="J29:P29"/>
+    <mergeCell ref="BE70:BG70"/>
     <mergeCell ref="X48:AD48"/>
     <mergeCell ref="AE23:AF23"/>
     <mergeCell ref="AC6:AE6"/>
@@ -15921,9 +18062,11 @@
     <mergeCell ref="Q7:S7"/>
     <mergeCell ref="AM26:AO26"/>
     <mergeCell ref="J24:P24"/>
+    <mergeCell ref="BB75:BD75"/>
     <mergeCell ref="AG51:AI51"/>
     <mergeCell ref="Q20:W20"/>
     <mergeCell ref="B47:D47"/>
+    <mergeCell ref="E70:I70"/>
     <mergeCell ref="Q14:W14"/>
     <mergeCell ref="B59:D59"/>
     <mergeCell ref="E57:I57"/>
@@ -15933,10 +18076,12 @@
     <mergeCell ref="AS54:AU54"/>
     <mergeCell ref="E32:I32"/>
     <mergeCell ref="J26:P26"/>
+    <mergeCell ref="BH66:BJ66"/>
     <mergeCell ref="AS41:AU41"/>
     <mergeCell ref="AE49:AF49"/>
     <mergeCell ref="AY13:BA13"/>
     <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="AG65:AI65"/>
     <mergeCell ref="E47:I47"/>
     <mergeCell ref="BB39:BD39"/>
     <mergeCell ref="B48:D48"/>
@@ -15945,6 +18090,7 @@
     <mergeCell ref="AP38:AR38"/>
     <mergeCell ref="X41:AD41"/>
     <mergeCell ref="AS43:AU43"/>
+    <mergeCell ref="BH68:BJ68"/>
     <mergeCell ref="AY63:BA63"/>
     <mergeCell ref="BE25:BG25"/>
     <mergeCell ref="BK38:BQ38"/>
@@ -15958,8 +18104,12 @@
     <mergeCell ref="J50:P50"/>
     <mergeCell ref="AM39:AO39"/>
     <mergeCell ref="AP40:AR40"/>
+    <mergeCell ref="BH67:BJ67"/>
+    <mergeCell ref="BE71:BG71"/>
     <mergeCell ref="BK63:BQ63"/>
     <mergeCell ref="AJ15:AL15"/>
+    <mergeCell ref="AY67:BA67"/>
+    <mergeCell ref="BB72:BD72"/>
     <mergeCell ref="Q13:W13"/>
     <mergeCell ref="AG19:AI19"/>
     <mergeCell ref="X36:AD36"/>
@@ -15967,7 +18117,12 @@
     <mergeCell ref="J44:P44"/>
     <mergeCell ref="Q25:W25"/>
     <mergeCell ref="AV37:AX37"/>
+    <mergeCell ref="BB65:BD65"/>
+    <mergeCell ref="BE66:BG66"/>
+    <mergeCell ref="AY69:BA69"/>
     <mergeCell ref="E60:I60"/>
+    <mergeCell ref="Q71:W71"/>
+    <mergeCell ref="X67:AD67"/>
     <mergeCell ref="J37:P37"/>
     <mergeCell ref="AV60:AX60"/>
     <mergeCell ref="Q33:W33"/>
@@ -15985,15 +18140,19 @@
     <mergeCell ref="AS29:AU29"/>
     <mergeCell ref="X62:AD62"/>
     <mergeCell ref="AE37:AF37"/>
+    <mergeCell ref="B66:D66"/>
     <mergeCell ref="BH16:BJ16"/>
     <mergeCell ref="AM29:AO29"/>
     <mergeCell ref="BB19:BD19"/>
     <mergeCell ref="AM23:AO23"/>
     <mergeCell ref="AE24:AF24"/>
+    <mergeCell ref="J70:P70"/>
     <mergeCell ref="A28:BQ28"/>
     <mergeCell ref="AS44:AU44"/>
     <mergeCell ref="AV27:AX27"/>
     <mergeCell ref="AS31:AU31"/>
+    <mergeCell ref="AM71:AO71"/>
+    <mergeCell ref="AG72:AI72"/>
     <mergeCell ref="BH18:BJ18"/>
     <mergeCell ref="J32:P32"/>
     <mergeCell ref="J63:P63"/>
@@ -16001,14 +18160,17 @@
     <mergeCell ref="AY38:BA38"/>
     <mergeCell ref="Q22:W22"/>
     <mergeCell ref="BB58:BD58"/>
+    <mergeCell ref="B67:D67"/>
     <mergeCell ref="B61:D61"/>
     <mergeCell ref="J47:P47"/>
     <mergeCell ref="AV58:AX58"/>
     <mergeCell ref="BB20:BD20"/>
     <mergeCell ref="BB14:BD14"/>
     <mergeCell ref="AY24:BA24"/>
+    <mergeCell ref="E71:I71"/>
     <mergeCell ref="BK17:BQ17"/>
     <mergeCell ref="BB60:BD60"/>
+    <mergeCell ref="B69:D69"/>
     <mergeCell ref="AP30:AR30"/>
     <mergeCell ref="AP59:AR59"/>
     <mergeCell ref="AJ30:AL30"/>
@@ -16034,26 +18196,36 @@
     <mergeCell ref="AP56:AR56"/>
     <mergeCell ref="AG20:AI20"/>
     <mergeCell ref="B16:D16"/>
+    <mergeCell ref="BE68:BG68"/>
     <mergeCell ref="AP43:AR43"/>
     <mergeCell ref="AM53:AO53"/>
+    <mergeCell ref="BE74:BG74"/>
     <mergeCell ref="AM47:AO47"/>
     <mergeCell ref="B10:D11"/>
     <mergeCell ref="J45:P45"/>
     <mergeCell ref="Q35:W35"/>
     <mergeCell ref="AM19:AO19"/>
+    <mergeCell ref="BB71:BD71"/>
     <mergeCell ref="AM46:AO46"/>
     <mergeCell ref="AG22:AI22"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="AJ23:AL23"/>
+    <mergeCell ref="E66:I66"/>
+    <mergeCell ref="AV71:AX71"/>
     <mergeCell ref="E53:I53"/>
+    <mergeCell ref="AE70:AF70"/>
+    <mergeCell ref="AY72:BA72"/>
     <mergeCell ref="AM48:AO48"/>
+    <mergeCell ref="Q74:W74"/>
     <mergeCell ref="Q49:W49"/>
+    <mergeCell ref="E68:I68"/>
     <mergeCell ref="BK43:BQ43"/>
     <mergeCell ref="AM44:AO44"/>
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="AF6:AH6"/>
     <mergeCell ref="AE32:AF32"/>
     <mergeCell ref="AV48:AX48"/>
+    <mergeCell ref="E67:I67"/>
     <mergeCell ref="AY14:BA14"/>
     <mergeCell ref="AJ18:AL18"/>
     <mergeCell ref="J51:P51"/>
@@ -16066,12 +18238,16 @@
     <mergeCell ref="Q6:S6"/>
     <mergeCell ref="BK34:BQ34"/>
     <mergeCell ref="AY59:BA59"/>
+    <mergeCell ref="AS70:AU70"/>
+    <mergeCell ref="J71:P71"/>
+    <mergeCell ref="X72:AD72"/>
     <mergeCell ref="J58:P58"/>
     <mergeCell ref="AS32:AU32"/>
     <mergeCell ref="AM45:AO45"/>
     <mergeCell ref="AJ49:AL49"/>
     <mergeCell ref="AP11:AR11"/>
     <mergeCell ref="BH19:BJ19"/>
+    <mergeCell ref="X70:AD70"/>
     <mergeCell ref="BB22:BD22"/>
     <mergeCell ref="BE23:BG23"/>
     <mergeCell ref="AJ36:AL36"/>
@@ -16085,6 +18261,7 @@
     <mergeCell ref="BK61:BQ61"/>
     <mergeCell ref="AJ44:AL44"/>
     <mergeCell ref="Q54:W54"/>
+    <mergeCell ref="AS65:AU65"/>
     <mergeCell ref="BE18:BG18"/>
     <mergeCell ref="AY27:BA27"/>
     <mergeCell ref="AJ31:AL31"/>
@@ -16093,8 +18270,10 @@
     <mergeCell ref="AM51:AO51"/>
     <mergeCell ref="Q23:W23"/>
     <mergeCell ref="B62:D62"/>
+    <mergeCell ref="AV66:AX66"/>
     <mergeCell ref="X19:AD19"/>
     <mergeCell ref="AE60:AF60"/>
+    <mergeCell ref="B72:D72"/>
     <mergeCell ref="AS58:AU58"/>
     <mergeCell ref="AG34:AI34"/>
     <mergeCell ref="AV59:AX59"/>
@@ -16109,6 +18288,7 @@
     <mergeCell ref="BK62:BQ62"/>
     <mergeCell ref="BE36:BG36"/>
     <mergeCell ref="BH37:BJ37"/>
+    <mergeCell ref="B70:D70"/>
     <mergeCell ref="AE45:AF45"/>
     <mergeCell ref="X58:AD58"/>
     <mergeCell ref="AS60:AU60"/>
@@ -16118,7 +18298,9 @@
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="AP51:AR51"/>
     <mergeCell ref="AG59:AI59"/>
+    <mergeCell ref="J66:P66"/>
     <mergeCell ref="BK51:BQ51"/>
+    <mergeCell ref="AM67:AO67"/>
     <mergeCell ref="X60:AD60"/>
     <mergeCell ref="AM61:AO61"/>
     <mergeCell ref="B17:D17"/>
@@ -16131,7 +18313,9 @@
     <mergeCell ref="BB35:BD35"/>
     <mergeCell ref="BH51:BJ51"/>
     <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AP65:AR65"/>
     <mergeCell ref="AM20:AO20"/>
+    <mergeCell ref="AM69:AO69"/>
     <mergeCell ref="AJ24:AL24"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="J61:P61"/>
@@ -16141,6 +18325,7 @@
     <mergeCell ref="AM35:AO35"/>
     <mergeCell ref="AJ26:AL26"/>
     <mergeCell ref="AS13:AU13"/>
+    <mergeCell ref="E69:I69"/>
     <mergeCell ref="AP17:AR17"/>
     <mergeCell ref="AY40:BA40"/>
     <mergeCell ref="A12:BQ12"/>
@@ -16151,7 +18336,9 @@
     <mergeCell ref="X13:AD13"/>
     <mergeCell ref="AS15:AU15"/>
     <mergeCell ref="AE48:AF48"/>
+    <mergeCell ref="AP75:AR75"/>
     <mergeCell ref="BH27:BJ27"/>
+    <mergeCell ref="BK75:BQ75"/>
     <mergeCell ref="BE37:BG37"/>
     <mergeCell ref="AJ50:AL50"/>
     <mergeCell ref="BH20:BJ20"/>
@@ -16161,6 +18348,8 @@
     <mergeCell ref="BH25:BJ25"/>
     <mergeCell ref="AM38:AO38"/>
     <mergeCell ref="AG41:AI41"/>
+    <mergeCell ref="BH69:BJ69"/>
+    <mergeCell ref="E72:I72"/>
     <mergeCell ref="BH35:BJ35"/>
     <mergeCell ref="AP39:AR39"/>
     <mergeCell ref="AP14:AR14"/>
@@ -16180,12 +18369,16 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="AG49:AI49"/>
     <mergeCell ref="AE51:AF51"/>
+    <mergeCell ref="AV67:AX67"/>
     <mergeCell ref="BB29:BD29"/>
     <mergeCell ref="BB23:BD23"/>
     <mergeCell ref="E24:I24"/>
     <mergeCell ref="AG36:AI36"/>
     <mergeCell ref="B13:D13"/>
+    <mergeCell ref="Q70:W70"/>
+    <mergeCell ref="AE66:AF66"/>
     <mergeCell ref="Q45:W45"/>
+    <mergeCell ref="AV69:AX69"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="BB31:BD31"/>
     <mergeCell ref="Q32:W32"/>
@@ -16194,16 +18387,22 @@
     <mergeCell ref="BH38:BJ38"/>
     <mergeCell ref="Q47:W47"/>
     <mergeCell ref="BH13:BJ13"/>
+    <mergeCell ref="AS66:AU66"/>
     <mergeCell ref="E19:I19"/>
     <mergeCell ref="BE52:BG52"/>
+    <mergeCell ref="BK65:BQ65"/>
+    <mergeCell ref="J67:P67"/>
     <mergeCell ref="BB56:BD56"/>
     <mergeCell ref="AE61:AF61"/>
+    <mergeCell ref="AE67:AF67"/>
     <mergeCell ref="AF7:AH7"/>
     <mergeCell ref="BH15:BJ15"/>
     <mergeCell ref="AY30:BA30"/>
+    <mergeCell ref="AS68:AU68"/>
     <mergeCell ref="AJ32:AL32"/>
     <mergeCell ref="AJ63:AL63"/>
     <mergeCell ref="AP25:AR25"/>
+    <mergeCell ref="J69:P69"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="AY46:BA46"/>
     <mergeCell ref="BB57:BD57"/>
@@ -16214,6 +18413,7 @@
     <mergeCell ref="Q63:W63"/>
     <mergeCell ref="AJ40:AL40"/>
     <mergeCell ref="Q50:W50"/>
+    <mergeCell ref="AM72:AO72"/>
     <mergeCell ref="AJ27:AL27"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="AY41:BA41"/>
@@ -16233,6 +18433,7 @@
     <mergeCell ref="AE16:AF16"/>
     <mergeCell ref="AG32:AI32"/>
     <mergeCell ref="X35:AD35"/>
+    <mergeCell ref="A64:BQ64"/>
     <mergeCell ref="AE10:AF11"/>
     <mergeCell ref="BH43:BJ43"/>
     <mergeCell ref="BE47:BG47"/>
@@ -16260,6 +18461,7 @@
     <mergeCell ref="AY34:BA34"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="J19:P19"/>
+    <mergeCell ref="BB70:BD70"/>
     <mergeCell ref="BH59:BJ59"/>
     <mergeCell ref="AY25:BA25"/>
     <mergeCell ref="AS34:AU34"/>
@@ -16271,15 +18473,20 @@
     <mergeCell ref="AS49:AU49"/>
     <mergeCell ref="X34:AD34"/>
     <mergeCell ref="AS30:AU30"/>
+    <mergeCell ref="AE69:AF69"/>
     <mergeCell ref="BB47:BD47"/>
     <mergeCell ref="AG60:AI60"/>
     <mergeCell ref="N7:P7"/>
     <mergeCell ref="BH54:BJ54"/>
+    <mergeCell ref="AJ71:AL71"/>
     <mergeCell ref="AP33:AR33"/>
+    <mergeCell ref="BK71:BQ71"/>
     <mergeCell ref="BH41:BJ41"/>
     <mergeCell ref="X30:AD30"/>
     <mergeCell ref="BE45:BG45"/>
     <mergeCell ref="AJ58:AL58"/>
+    <mergeCell ref="BH65:BJ65"/>
+    <mergeCell ref="AS69:AU69"/>
     <mergeCell ref="E22:I22"/>
     <mergeCell ref="BH56:BJ56"/>
     <mergeCell ref="X29:AD29"/>
@@ -16289,12 +18496,18 @@
     <mergeCell ref="BE59:BG59"/>
     <mergeCell ref="AY62:BA62"/>
     <mergeCell ref="BB63:BD63"/>
+    <mergeCell ref="AJ66:AL66"/>
     <mergeCell ref="BE46:BG46"/>
+    <mergeCell ref="AG70:AI70"/>
+    <mergeCell ref="AE72:AF72"/>
     <mergeCell ref="BB50:BD50"/>
     <mergeCell ref="X54:AD54"/>
+    <mergeCell ref="AP74:AR74"/>
     <mergeCell ref="BK20:BQ20"/>
     <mergeCell ref="B34:D34"/>
+    <mergeCell ref="AJ68:AL68"/>
     <mergeCell ref="AV19:AX19"/>
+    <mergeCell ref="Q66:W66"/>
     <mergeCell ref="AS23:AU23"/>
     <mergeCell ref="E38:I38"/>
     <mergeCell ref="AY51:BA51"/>
@@ -16303,7 +18516,9 @@
     <mergeCell ref="BK22:BQ22"/>
     <mergeCell ref="E13:I13"/>
     <mergeCell ref="X43:AD43"/>
+    <mergeCell ref="AG71:AI71"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="Q68:W68"/>
     <mergeCell ref="E40:I40"/>
     <mergeCell ref="BK15:BQ15"/>
     <mergeCell ref="AE17:AF17"/>
@@ -16321,6 +18536,7 @@
     <mergeCell ref="AJ59:AL59"/>
     <mergeCell ref="B54:D54"/>
     <mergeCell ref="AS26:AU26"/>
+    <mergeCell ref="AE65:AF65"/>
     <mergeCell ref="AJ46:AL46"/>
     <mergeCell ref="J27:P27"/>
     <mergeCell ref="AG25:AI25"/>
@@ -16334,6 +18550,7 @@
     <mergeCell ref="AJ61:AL61"/>
     <mergeCell ref="AV47:AX47"/>
     <mergeCell ref="B43:D43"/>
+    <mergeCell ref="AY75:BA75"/>
     <mergeCell ref="BE51:BG51"/>
     <mergeCell ref="AY50:BA50"/>
     <mergeCell ref="BK33:BQ33"/>
@@ -16341,6 +18558,7 @@
     <mergeCell ref="J22:P22"/>
     <mergeCell ref="BH62:BJ62"/>
     <mergeCell ref="AV38:AX38"/>
+    <mergeCell ref="X75:AD75"/>
     <mergeCell ref="AY52:BA52"/>
     <mergeCell ref="N8:P8"/>
     <mergeCell ref="BK35:BQ35"/>
@@ -16362,10 +18580,15 @@
     <mergeCell ref="AS37:AU37"/>
     <mergeCell ref="AE14:AF14"/>
     <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="BE67:BG67"/>
+    <mergeCell ref="AJ74:AL74"/>
     <mergeCell ref="J38:P38"/>
+    <mergeCell ref="BK74:BQ74"/>
+    <mergeCell ref="AM75:AO75"/>
     <mergeCell ref="K7:M7"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="E30:I30"/>
+    <mergeCell ref="BE69:BG69"/>
     <mergeCell ref="AG15:AI15"/>
     <mergeCell ref="AJ16:AL16"/>
     <mergeCell ref="X32:AD32"/>
@@ -16376,19 +18599,28 @@
     <mergeCell ref="J40:P40"/>
     <mergeCell ref="BE62:BG62"/>
     <mergeCell ref="J15:P15"/>
+    <mergeCell ref="AY65:BA65"/>
     <mergeCell ref="AM41:AO41"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="BB66:BD66"/>
     <mergeCell ref="E61:I61"/>
+    <mergeCell ref="Q67:W67"/>
+    <mergeCell ref="B75:D75"/>
     <mergeCell ref="AV35:AX35"/>
     <mergeCell ref="AJ11:AL11"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="X49:AD49"/>
     <mergeCell ref="E54:I54"/>
+    <mergeCell ref="BB68:BD68"/>
     <mergeCell ref="AV22:AX22"/>
     <mergeCell ref="AY23:BA23"/>
     <mergeCell ref="AS63:AU63"/>
     <mergeCell ref="E41:I41"/>
     <mergeCell ref="J35:P35"/>
+    <mergeCell ref="X65:AD65"/>
+    <mergeCell ref="AM66:AO66"/>
+    <mergeCell ref="Q69:W69"/>
+    <mergeCell ref="BH75:BJ75"/>
     <mergeCell ref="AE27:AF27"/>
     <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="B39:D39"/>
@@ -16406,6 +18638,8 @@
     <mergeCell ref="BK29:BQ29"/>
     <mergeCell ref="AS40:AU40"/>
     <mergeCell ref="X50:AD50"/>
+    <mergeCell ref="AM68:AO68"/>
+    <mergeCell ref="A73:BQ73"/>
     <mergeCell ref="BH52:BJ52"/>
     <mergeCell ref="AS27:AU27"/>
     <mergeCell ref="AP31:AR31"/>
@@ -16420,12 +18654,15 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="Q16:W16"/>
     <mergeCell ref="AV40:AX40"/>
+    <mergeCell ref="B65:D65"/>
     <mergeCell ref="T7:V7"/>
+    <mergeCell ref="J72:P72"/>
     <mergeCell ref="X52:AD52"/>
     <mergeCell ref="Q24:W24"/>
     <mergeCell ref="AG30:AI30"/>
     <mergeCell ref="Q18:W18"/>
     <mergeCell ref="BK49:BQ49"/>
+    <mergeCell ref="AG67:AI67"/>
     <mergeCell ref="B63:D63"/>
     <mergeCell ref="AM37:AO37"/>
     <mergeCell ref="AE38:AF38"/>
@@ -16438,6 +18675,7 @@
     <mergeCell ref="AE13:AF13"/>
     <mergeCell ref="AS45:AU45"/>
     <mergeCell ref="BK57:BQ57"/>
+    <mergeCell ref="AG69:AI69"/>
     <mergeCell ref="AE40:AF40"/>
     <mergeCell ref="X53:AD53"/>
     <mergeCell ref="X47:AD47"/>
@@ -16453,28 +18691,39 @@
     <mergeCell ref="AM62:AO62"/>
     <mergeCell ref="AJ17:AL17"/>
     <mergeCell ref="AM56:AO56"/>
+    <mergeCell ref="BB74:BD74"/>
     <mergeCell ref="J54:P54"/>
     <mergeCell ref="AM43:AO43"/>
     <mergeCell ref="J41:P41"/>
     <mergeCell ref="Q44:W44"/>
+    <mergeCell ref="BB67:BD67"/>
     <mergeCell ref="AV43:AX43"/>
     <mergeCell ref="AJ19:AL19"/>
+    <mergeCell ref="AY71:BA71"/>
     <mergeCell ref="E62:I62"/>
     <mergeCell ref="J56:P56"/>
+    <mergeCell ref="BE72:BG72"/>
     <mergeCell ref="AY58:BA58"/>
+    <mergeCell ref="AS71:AU71"/>
     <mergeCell ref="J43:P43"/>
     <mergeCell ref="AM57:AO57"/>
     <mergeCell ref="X25:AD25"/>
+    <mergeCell ref="BB69:BD69"/>
     <mergeCell ref="AG16:AI16"/>
+    <mergeCell ref="AV72:AX72"/>
+    <mergeCell ref="X71:AD71"/>
     <mergeCell ref="E51:I51"/>
     <mergeCell ref="BK31:BQ31"/>
     <mergeCell ref="AG18:AI18"/>
     <mergeCell ref="BE17:BG17"/>
+    <mergeCell ref="AP70:AR70"/>
     <mergeCell ref="AM25:AO25"/>
     <mergeCell ref="N6:P6"/>
+    <mergeCell ref="E65:I65"/>
     <mergeCell ref="J59:P59"/>
     <mergeCell ref="AP32:AR32"/>
     <mergeCell ref="BK45:BQ45"/>
+    <mergeCell ref="X66:AD66"/>
     <mergeCell ref="BE19:BG19"/>
     <mergeCell ref="BK32:BQ32"/>
     <mergeCell ref="AM33:AO33"/>
@@ -16488,6 +18737,7 @@
     <mergeCell ref="AE30:AF30"/>
     <mergeCell ref="Q26:W26"/>
     <mergeCell ref="AG10:AU10"/>
+    <mergeCell ref="B71:D71"/>
     <mergeCell ref="AG44:AI44"/>
     <mergeCell ref="AV62:AX62"/>
     <mergeCell ref="BE14:BG14"/>
@@ -16497,16 +18747,17 @@
     <mergeCell ref="AG31:AI31"/>
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="B58:D58"/>
+    <mergeCell ref="E75:I75"/>
     <mergeCell ref="BE60:BG60"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE20 AE22:AE27 AE29:AE41 AE43:AE54 AE56:AE63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE20 AE22:AE27 AE29:AE41 AE43:AE54 AE56:AE63 AE65:AE72 AE74:AE75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG20 AG22:AG27 AG29:AG41 AG43:AG54 AG56:AG63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG20 AG22:AG27 AG29:AG41 AG43:AG54 AG56:AG63 AG65:AG72 AG74:AG75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV20 AV22:AV27 AV29:AV41 AV43:AV54 AV56:AV63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV20 AV22:AV27 AV29:AV41 AV43:AV54 AV56:AV63 AV65:AV72 AV74:AV75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
